--- a/CPRD Raw Analysis/Results/Output_yearly_visits_Raw-Boot.xlsx
+++ b/CPRD Raw Analysis/Results/Output_yearly_visits_Raw-Boot.xlsx
@@ -384,13 +384,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.175</v>
+        <v>13.681</v>
       </c>
       <c r="C2">
-        <v>15.989</v>
+        <v>13.48</v>
       </c>
       <c r="D2">
-        <v>16.361</v>
+        <v>13.892</v>
       </c>
     </row>
     <row r="3">
@@ -398,13 +398,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11.295</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="C3">
-        <v>11.126</v>
+        <v>9.042</v>
       </c>
       <c r="D3">
-        <v>11.46</v>
+        <v>9.394</v>
       </c>
     </row>
   </sheetData>
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>16.43</v>
+        <v>14.064</v>
       </c>
       <c r="C2">
-        <v>16.246</v>
+        <v>13.865</v>
       </c>
       <c r="D2">
-        <v>16.608</v>
+        <v>14.267</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11.473</v>
+        <v>9.478</v>
       </c>
       <c r="C3">
-        <v>11.314</v>
+        <v>9.292</v>
       </c>
       <c r="D3">
-        <v>11.633</v>
+        <v>9.663</v>
       </c>
     </row>
   </sheetData>
@@ -504,13 +504,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>17.01</v>
+        <v>16.029</v>
       </c>
       <c r="C2">
-        <v>16.814</v>
+        <v>15.806</v>
       </c>
       <c r="D2">
-        <v>17.195</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="3">
@@ -518,13 +518,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>11.975</v>
+        <v>11.308</v>
       </c>
       <c r="C3">
-        <v>11.802</v>
+        <v>11.102</v>
       </c>
       <c r="D3">
-        <v>12.137</v>
+        <v>11.519</v>
       </c>
     </row>
   </sheetData>
@@ -564,13 +564,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>17.201</v>
+        <v>16.254</v>
       </c>
       <c r="C2">
-        <v>17.009</v>
+        <v>16.025</v>
       </c>
       <c r="D2">
-        <v>17.39</v>
+        <v>16.479</v>
       </c>
     </row>
     <row r="3">
@@ -578,13 +578,13 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>12.11</v>
+        <v>11.486</v>
       </c>
       <c r="C3">
-        <v>11.934</v>
+        <v>11.283</v>
       </c>
       <c r="D3">
-        <v>12.282</v>
+        <v>11.688</v>
       </c>
     </row>
   </sheetData>
